--- a/figures/supplemental_tables_v2/SupTable8_HRDTimer_estimates.xlsx
+++ b/figures/supplemental_tables_v2/SupTable8_HRDTimer_estimates.xlsx
@@ -21532,7 +21532,9 @@
           <t>BRCA2</t>
         </is>
       </c>
-      <c r="Q93" t="inlineStr"/>
+      <c r="Q93" t="n">
+        <v>1</v>
+      </c>
       <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr"/>
       <c r="T93" t="inlineStr"/>
@@ -21718,7 +21720,9 @@
           <t>BRCA1</t>
         </is>
       </c>
-      <c r="Q94" t="inlineStr"/>
+      <c r="Q94" t="n">
+        <v>1</v>
+      </c>
       <c r="R94" t="inlineStr"/>
       <c r="S94" t="inlineStr"/>
       <c r="T94" t="inlineStr"/>
@@ -21904,7 +21908,9 @@
           <t>BRCA2</t>
         </is>
       </c>
-      <c r="Q95" t="inlineStr"/>
+      <c r="Q95" t="n">
+        <v>1</v>
+      </c>
       <c r="R95" t="inlineStr"/>
       <c r="S95" t="inlineStr"/>
       <c r="T95" t="inlineStr"/>
@@ -22082,7 +22088,9 @@
           <t>BRCA1</t>
         </is>
       </c>
-      <c r="Q96" t="inlineStr"/>
+      <c r="Q96" t="n">
+        <v>1</v>
+      </c>
       <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr"/>
       <c r="T96" t="inlineStr"/>
@@ -22256,7 +22264,9 @@
           <t>BRCA1</t>
         </is>
       </c>
-      <c r="Q97" t="inlineStr"/>
+      <c r="Q97" t="n">
+        <v>1</v>
+      </c>
       <c r="R97" t="inlineStr"/>
       <c r="S97" t="inlineStr"/>
       <c r="T97" t="inlineStr"/>
@@ -22442,7 +22452,9 @@
           <t>BRCA2</t>
         </is>
       </c>
-      <c r="Q98" t="inlineStr"/>
+      <c r="Q98" t="n">
+        <v>1</v>
+      </c>
       <c r="R98" t="inlineStr"/>
       <c r="S98" t="inlineStr"/>
       <c r="T98" t="inlineStr"/>
@@ -22628,7 +22640,9 @@
           <t>BRCA2</t>
         </is>
       </c>
-      <c r="Q99" t="inlineStr"/>
+      <c r="Q99" t="n">
+        <v>1</v>
+      </c>
       <c r="R99" t="inlineStr"/>
       <c r="S99" t="inlineStr"/>
       <c r="T99" t="inlineStr"/>
@@ -22826,7 +22840,9 @@
           <t>BRCA2</t>
         </is>
       </c>
-      <c r="Q100" t="inlineStr"/>
+      <c r="Q100" t="n">
+        <v>0</v>
+      </c>
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="inlineStr"/>
       <c r="T100" t="inlineStr"/>
@@ -23004,7 +23020,9 @@
           <t>BRCA1</t>
         </is>
       </c>
-      <c r="Q101" t="inlineStr"/>
+      <c r="Q101" t="n">
+        <v>1</v>
+      </c>
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="inlineStr"/>
       <c r="T101" t="inlineStr"/>
@@ -23190,7 +23208,9 @@
           <t>BRCA2</t>
         </is>
       </c>
-      <c r="Q102" t="inlineStr"/>
+      <c r="Q102" t="n">
+        <v>0</v>
+      </c>
       <c r="R102" t="inlineStr"/>
       <c r="S102" t="inlineStr"/>
       <c r="T102" t="inlineStr"/>
@@ -23376,7 +23396,9 @@
           <t>BRCA1</t>
         </is>
       </c>
-      <c r="Q103" t="inlineStr"/>
+      <c r="Q103" t="n">
+        <v>1</v>
+      </c>
       <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr"/>
       <c r="T103" t="inlineStr"/>
@@ -23554,7 +23576,9 @@
           <t>BRCA1</t>
         </is>
       </c>
-      <c r="Q104" t="inlineStr"/>
+      <c r="Q104" t="n">
+        <v>1</v>
+      </c>
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr"/>
       <c r="T104" t="inlineStr"/>
@@ -23740,7 +23764,9 @@
           <t>BRCA1</t>
         </is>
       </c>
-      <c r="Q105" t="inlineStr"/>
+      <c r="Q105" t="n">
+        <v>1</v>
+      </c>
       <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr"/>
       <c r="T105" t="inlineStr"/>
@@ -23930,7 +23956,9 @@
           <t>BRCA2</t>
         </is>
       </c>
-      <c r="Q106" t="inlineStr"/>
+      <c r="Q106" t="n">
+        <v>0</v>
+      </c>
       <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr"/>
       <c r="T106" t="inlineStr"/>
@@ -24116,7 +24144,9 @@
           <t>BRCA2</t>
         </is>
       </c>
-      <c r="Q107" t="inlineStr"/>
+      <c r="Q107" t="n">
+        <v>0</v>
+      </c>
       <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr"/>
       <c r="T107" t="inlineStr"/>
@@ -24294,7 +24324,9 @@
           <t>BRCA1</t>
         </is>
       </c>
-      <c r="Q108" t="inlineStr"/>
+      <c r="Q108" t="n">
+        <v>1</v>
+      </c>
       <c r="R108" t="inlineStr"/>
       <c r="S108" t="inlineStr"/>
       <c r="T108" t="inlineStr"/>
@@ -24468,7 +24500,9 @@
           <t>BRCA2</t>
         </is>
       </c>
-      <c r="Q109" t="inlineStr"/>
+      <c r="Q109" t="n">
+        <v>1</v>
+      </c>
       <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr"/>
       <c r="T109" t="inlineStr"/>
@@ -24654,7 +24688,9 @@
           <t>BRCA2</t>
         </is>
       </c>
-      <c r="Q110" t="inlineStr"/>
+      <c r="Q110" t="n">
+        <v>1</v>
+      </c>
       <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr"/>
       <c r="T110" t="inlineStr"/>
@@ -24840,7 +24876,9 @@
           <t>BRCA1</t>
         </is>
       </c>
-      <c r="Q111" t="inlineStr"/>
+      <c r="Q111" t="n">
+        <v>1</v>
+      </c>
       <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr"/>
       <c r="T111" t="inlineStr"/>
@@ -25026,7 +25064,9 @@
           <t>BRCA2</t>
         </is>
       </c>
-      <c r="Q112" t="inlineStr"/>
+      <c r="Q112" t="n">
+        <v>1</v>
+      </c>
       <c r="R112" t="inlineStr"/>
       <c r="S112" t="inlineStr"/>
       <c r="T112" t="inlineStr"/>
@@ -25224,7 +25264,9 @@
           <t>BRCA2</t>
         </is>
       </c>
-      <c r="Q113" t="inlineStr"/>
+      <c r="Q113" t="n">
+        <v>0</v>
+      </c>
       <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr"/>
       <c r="T113" t="inlineStr"/>
@@ -25410,7 +25452,9 @@
           <t>BRCA2</t>
         </is>
       </c>
-      <c r="Q114" t="inlineStr"/>
+      <c r="Q114" t="n">
+        <v>1</v>
+      </c>
       <c r="R114" t="inlineStr"/>
       <c r="S114" t="inlineStr"/>
       <c r="T114" t="inlineStr"/>
@@ -25608,7 +25652,9 @@
           <t>BRCA2</t>
         </is>
       </c>
-      <c r="Q115" t="inlineStr"/>
+      <c r="Q115" t="n">
+        <v>1</v>
+      </c>
       <c r="R115" t="inlineStr"/>
       <c r="S115" t="inlineStr"/>
       <c r="T115" t="inlineStr"/>
@@ -25794,7 +25840,9 @@
           <t>BRCA2</t>
         </is>
       </c>
-      <c r="Q116" t="inlineStr"/>
+      <c r="Q116" t="n">
+        <v>1</v>
+      </c>
       <c r="R116" t="inlineStr"/>
       <c r="S116" t="inlineStr"/>
       <c r="T116" t="inlineStr"/>
@@ -25968,7 +26016,9 @@
           <t>BRCA2</t>
         </is>
       </c>
-      <c r="Q117" t="inlineStr"/>
+      <c r="Q117" t="n">
+        <v>0</v>
+      </c>
       <c r="R117" t="inlineStr"/>
       <c r="S117" t="inlineStr"/>
       <c r="T117" t="inlineStr"/>
@@ -26154,7 +26204,9 @@
           <t>BRCA1</t>
         </is>
       </c>
-      <c r="Q118" t="inlineStr"/>
+      <c r="Q118" t="n">
+        <v>1</v>
+      </c>
       <c r="R118" t="inlineStr"/>
       <c r="S118" t="inlineStr"/>
       <c r="T118" t="inlineStr"/>
@@ -26340,7 +26392,9 @@
           <t>BRCA2</t>
         </is>
       </c>
-      <c r="Q119" t="inlineStr"/>
+      <c r="Q119" t="n">
+        <v>1</v>
+      </c>
       <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr"/>
       <c r="T119" t="inlineStr"/>
@@ -26526,7 +26580,9 @@
           <t>BRCA2</t>
         </is>
       </c>
-      <c r="Q120" t="inlineStr"/>
+      <c r="Q120" t="n">
+        <v>0</v>
+      </c>
       <c r="R120" t="inlineStr"/>
       <c r="S120" t="inlineStr"/>
       <c r="T120" t="inlineStr"/>
@@ -26700,7 +26756,9 @@
           <t>BRCA2</t>
         </is>
       </c>
-      <c r="Q121" t="inlineStr"/>
+      <c r="Q121" t="n">
+        <v>1</v>
+      </c>
       <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr"/>
       <c r="T121" t="inlineStr"/>
@@ -26866,7 +26924,9 @@
           <t>BRCA2</t>
         </is>
       </c>
-      <c r="Q122" t="inlineStr"/>
+      <c r="Q122" t="n">
+        <v>1</v>
+      </c>
       <c r="R122" t="inlineStr"/>
       <c r="S122" t="inlineStr"/>
       <c r="T122" t="inlineStr"/>
@@ -27032,7 +27092,9 @@
           <t>BRCA1</t>
         </is>
       </c>
-      <c r="Q123" t="inlineStr"/>
+      <c r="Q123" t="n">
+        <v>1</v>
+      </c>
       <c r="R123" t="inlineStr"/>
       <c r="S123" t="inlineStr"/>
       <c r="T123" t="inlineStr"/>
@@ -27218,7 +27280,9 @@
           <t>BRCA2</t>
         </is>
       </c>
-      <c r="Q124" t="inlineStr"/>
+      <c r="Q124" t="n">
+        <v>1</v>
+      </c>
       <c r="R124" t="inlineStr"/>
       <c r="S124" t="inlineStr"/>
       <c r="T124" t="inlineStr"/>
@@ -27404,7 +27468,9 @@
           <t>BRCA1</t>
         </is>
       </c>
-      <c r="Q125" t="inlineStr"/>
+      <c r="Q125" t="n">
+        <v>1</v>
+      </c>
       <c r="R125" t="inlineStr"/>
       <c r="S125" t="inlineStr"/>
       <c r="T125" t="inlineStr"/>
@@ -27582,7 +27648,9 @@
           <t>BRCA2</t>
         </is>
       </c>
-      <c r="Q126" t="inlineStr"/>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
       <c r="R126" t="inlineStr"/>
       <c r="S126" t="inlineStr"/>
       <c r="T126" t="inlineStr"/>
@@ -27768,7 +27836,9 @@
           <t>BRCA2</t>
         </is>
       </c>
-      <c r="Q127" t="inlineStr"/>
+      <c r="Q127" t="n">
+        <v>0</v>
+      </c>
       <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr"/>
       <c r="T127" t="inlineStr"/>
@@ -27946,7 +28016,9 @@
           <t>BRCA1</t>
         </is>
       </c>
-      <c r="Q128" t="inlineStr"/>
+      <c r="Q128" t="n">
+        <v>1</v>
+      </c>
       <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr"/>
       <c r="T128" t="inlineStr"/>
@@ -28112,7 +28184,9 @@
           <t>BRCA1</t>
         </is>
       </c>
-      <c r="Q129" t="inlineStr"/>
+      <c r="Q129" t="n">
+        <v>1</v>
+      </c>
       <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr"/>
       <c r="T129" t="inlineStr"/>
@@ -28298,7 +28372,9 @@
           <t>BRCA2</t>
         </is>
       </c>
-      <c r="Q130" t="inlineStr"/>
+      <c r="Q130" t="n">
+        <v>1</v>
+      </c>
       <c r="R130" t="inlineStr"/>
       <c r="S130" t="inlineStr"/>
       <c r="T130" t="inlineStr"/>
@@ -28472,7 +28548,9 @@
           <t>BRCA1</t>
         </is>
       </c>
-      <c r="Q131" t="inlineStr"/>
+      <c r="Q131" t="n">
+        <v>1</v>
+      </c>
       <c r="R131" t="inlineStr"/>
       <c r="S131" t="inlineStr"/>
       <c r="T131" t="inlineStr"/>
@@ -28646,7 +28724,9 @@
           <t>BRCA1</t>
         </is>
       </c>
-      <c r="Q132" t="inlineStr"/>
+      <c r="Q132" t="n">
+        <v>1</v>
+      </c>
       <c r="R132" t="inlineStr"/>
       <c r="S132" t="inlineStr"/>
       <c r="T132" t="inlineStr"/>
@@ -28832,7 +28912,9 @@
           <t>BRCA1</t>
         </is>
       </c>
-      <c r="Q133" t="inlineStr"/>
+      <c r="Q133" t="n">
+        <v>1</v>
+      </c>
       <c r="R133" t="inlineStr"/>
       <c r="S133" t="inlineStr"/>
       <c r="T133" t="inlineStr"/>
@@ -29030,7 +29112,9 @@
           <t>BRCA1</t>
         </is>
       </c>
-      <c r="Q134" t="inlineStr"/>
+      <c r="Q134" t="n">
+        <v>0</v>
+      </c>
       <c r="R134" t="inlineStr"/>
       <c r="S134" t="inlineStr"/>
       <c r="T134" t="inlineStr"/>
@@ -29216,7 +29300,9 @@
           <t>BRCA2</t>
         </is>
       </c>
-      <c r="Q135" t="inlineStr"/>
+      <c r="Q135" t="n">
+        <v>1</v>
+      </c>
       <c r="R135" t="inlineStr"/>
       <c r="S135" t="inlineStr"/>
       <c r="T135" t="inlineStr"/>
@@ -29390,7 +29476,9 @@
           <t>BRCA2</t>
         </is>
       </c>
-      <c r="Q136" t="inlineStr"/>
+      <c r="Q136" t="n">
+        <v>0</v>
+      </c>
       <c r="R136" t="inlineStr"/>
       <c r="S136" t="inlineStr"/>
       <c r="T136" t="inlineStr"/>
@@ -29564,7 +29652,9 @@
           <t>BRCA2</t>
         </is>
       </c>
-      <c r="Q137" t="inlineStr"/>
+      <c r="Q137" t="n">
+        <v>1</v>
+      </c>
       <c r="R137" t="inlineStr"/>
       <c r="S137" t="inlineStr"/>
       <c r="T137" t="inlineStr"/>
@@ -29738,7 +29828,9 @@
           <t>BRCA1</t>
         </is>
       </c>
-      <c r="Q138" t="inlineStr"/>
+      <c r="Q138" t="n">
+        <v>1</v>
+      </c>
       <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr"/>
       <c r="T138" t="inlineStr"/>
@@ -29924,7 +30016,9 @@
           <t>BRCA2</t>
         </is>
       </c>
-      <c r="Q139" t="inlineStr"/>
+      <c r="Q139" t="n">
+        <v>1</v>
+      </c>
       <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr"/>
       <c r="T139" t="inlineStr"/>
@@ -30122,7 +30216,9 @@
           <t>BRCA1</t>
         </is>
       </c>
-      <c r="Q140" t="inlineStr"/>
+      <c r="Q140" t="n">
+        <v>1</v>
+      </c>
       <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr"/>
       <c r="T140" t="inlineStr"/>
@@ -30320,7 +30416,9 @@
           <t>BRCA2</t>
         </is>
       </c>
-      <c r="Q141" t="inlineStr"/>
+      <c r="Q141" t="n">
+        <v>0</v>
+      </c>
       <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr"/>
       <c r="T141" t="inlineStr"/>
@@ -30486,7 +30584,9 @@
           <t>BRCA1</t>
         </is>
       </c>
-      <c r="Q142" t="inlineStr"/>
+      <c r="Q142" t="n">
+        <v>1</v>
+      </c>
       <c r="R142" t="inlineStr"/>
       <c r="S142" t="inlineStr"/>
       <c r="T142" t="inlineStr"/>
@@ -30660,7 +30760,9 @@
           <t>BRCA2</t>
         </is>
       </c>
-      <c r="Q143" t="inlineStr"/>
+      <c r="Q143" t="n">
+        <v>0</v>
+      </c>
       <c r="R143" t="inlineStr"/>
       <c r="S143" t="inlineStr"/>
       <c r="T143" t="inlineStr"/>
@@ -30846,7 +30948,9 @@
           <t>BRCA2</t>
         </is>
       </c>
-      <c r="Q144" t="inlineStr"/>
+      <c r="Q144" t="n">
+        <v>1</v>
+      </c>
       <c r="R144" t="inlineStr"/>
       <c r="S144" t="inlineStr"/>
       <c r="T144" t="inlineStr"/>
@@ -31020,7 +31124,9 @@
           <t>BRCA2</t>
         </is>
       </c>
-      <c r="Q145" t="inlineStr"/>
+      <c r="Q145" t="n">
+        <v>0</v>
+      </c>
       <c r="R145" t="inlineStr"/>
       <c r="S145" t="inlineStr"/>
       <c r="T145" t="inlineStr"/>
@@ -31194,7 +31300,9 @@
           <t>BRCA2</t>
         </is>
       </c>
-      <c r="Q146" t="inlineStr"/>
+      <c r="Q146" t="n">
+        <v>0</v>
+      </c>
       <c r="R146" t="inlineStr"/>
       <c r="S146" t="inlineStr"/>
       <c r="T146" t="inlineStr"/>
@@ -31392,7 +31500,9 @@
           <t>BRCA1</t>
         </is>
       </c>
-      <c r="Q147" t="inlineStr"/>
+      <c r="Q147" t="n">
+        <v>1</v>
+      </c>
       <c r="R147" t="inlineStr"/>
       <c r="S147" t="inlineStr"/>
       <c r="T147" t="inlineStr"/>
@@ -31590,7 +31700,9 @@
           <t>BRCA2</t>
         </is>
       </c>
-      <c r="Q148" t="inlineStr"/>
+      <c r="Q148" t="n">
+        <v>0</v>
+      </c>
       <c r="R148" t="inlineStr"/>
       <c r="S148" t="inlineStr"/>
       <c r="T148" t="inlineStr"/>
